--- a/Assets/DataTables/Datas/__tables__.xlsx
+++ b/Assets/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\Development\Unity\Demos\MyFramework\Assets\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCBDE83-7BEA-41B6-A671-1D259F27BDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4A8F97-9D7A-4247-AB8C-9A828E553A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11655" yWindow="3645" windowWidth="13155" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -103,15 +103,39 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>demo.item.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Demo.TbItem</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Demo.Item</t>
+    <t>Store.TbStoreItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Store.StoreItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>store.store_item.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player.TbInventory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>player.inventory.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player.Inventory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Config.TbItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Config.Item</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>config.item.xlsx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -466,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -568,16 +592,44 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
         <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
